--- a/artfynd/A 37039-2026 artfynd.xlsx
+++ b/artfynd/A 37039-2026 artfynd.xlsx
@@ -818,7 +818,7 @@
         <v>136125287</v>
       </c>
       <c r="B3" t="n">
-        <v>101454</v>
+        <v>101457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>136125341</v>
       </c>
       <c r="B4" t="n">
-        <v>101454</v>
+        <v>101457</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>136125363</v>
       </c>
       <c r="B5" t="n">
-        <v>101454</v>
+        <v>101457</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>136109745</v>
       </c>
       <c r="B6" t="n">
-        <v>99321</v>
+        <v>99324</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>136125489</v>
       </c>
       <c r="B7" t="n">
-        <v>103638</v>
+        <v>103641</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 37039-2026 artfynd.xlsx
+++ b/artfynd/A 37039-2026 artfynd.xlsx
@@ -818,7 +818,7 @@
         <v>136125287</v>
       </c>
       <c r="B3" t="n">
-        <v>101457</v>
+        <v>101458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>136125341</v>
       </c>
       <c r="B4" t="n">
-        <v>101457</v>
+        <v>101458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>136125363</v>
       </c>
       <c r="B5" t="n">
-        <v>101457</v>
+        <v>101458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>136109745</v>
       </c>
       <c r="B6" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>136125489</v>
       </c>
       <c r="B7" t="n">
-        <v>103641</v>
+        <v>103642</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 37039-2026 artfynd.xlsx
+++ b/artfynd/A 37039-2026 artfynd.xlsx
@@ -818,7 +818,7 @@
         <v>136125287</v>
       </c>
       <c r="B3" t="n">
-        <v>101458</v>
+        <v>101463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>136125341</v>
       </c>
       <c r="B4" t="n">
-        <v>101458</v>
+        <v>101463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>136125363</v>
       </c>
       <c r="B5" t="n">
-        <v>101458</v>
+        <v>101463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>136109745</v>
       </c>
       <c r="B6" t="n">
-        <v>99325</v>
+        <v>99330</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>136125489</v>
       </c>
       <c r="B7" t="n">
-        <v>103642</v>
+        <v>103647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
